--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448826</v>
+        <v>122448814</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566628</v>
+        <v>566631</v>
       </c>
       <c r="R2" t="n">
-        <v>6417080</v>
+        <v>6417076</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
         <v>122448794</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448814</v>
+        <v>122448826</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566631</v>
+        <v>566628</v>
       </c>
       <c r="R4" t="n">
-        <v>6417076</v>
+        <v>6417080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122448814</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448794</v>
+        <v>122448826</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566615</v>
+        <v>566628</v>
       </c>
       <c r="R3" t="n">
-        <v>6417084</v>
+        <v>6417080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448826</v>
+        <v>122448794</v>
       </c>
       <c r="B4" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566628</v>
+        <v>566615</v>
       </c>
       <c r="R4" t="n">
-        <v>6417080</v>
+        <v>6417084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448814</v>
+        <v>122448826</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566631</v>
+        <v>566628</v>
       </c>
       <c r="R2" t="n">
-        <v>6417076</v>
+        <v>6417080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448826</v>
+        <v>122448814</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,11 +798,6 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -834,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566628</v>
+        <v>566631</v>
       </c>
       <c r="R3" t="n">
-        <v>6417080</v>
+        <v>6417076</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +890,7 @@
         <v>122448794</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,11 +904,6 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448826</v>
+        <v>122448794</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566628</v>
+        <v>566615</v>
       </c>
       <c r="R2" t="n">
-        <v>6417080</v>
+        <v>6417084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +789,7 @@
         <v>122448814</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,6 +803,11 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -887,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448794</v>
+        <v>122448826</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,6 +914,11 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -930,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566615</v>
+        <v>566628</v>
       </c>
       <c r="R4" t="n">
-        <v>6417084</v>
+        <v>6417080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448794</v>
+        <v>122448826</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566615</v>
+        <v>566628</v>
       </c>
       <c r="R2" t="n">
-        <v>6417084</v>
+        <v>6417080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
         <v>122448814</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448826</v>
+        <v>122448794</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566628</v>
+        <v>566615</v>
       </c>
       <c r="R4" t="n">
-        <v>6417080</v>
+        <v>6417084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448814</v>
+        <v>122448794</v>
       </c>
       <c r="B3" t="n">
         <v>98237</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566631</v>
+        <v>566615</v>
       </c>
       <c r="R3" t="n">
-        <v>6417076</v>
+        <v>6417084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448794</v>
+        <v>122448814</v>
       </c>
       <c r="B4" t="n">
         <v>98237</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566615</v>
+        <v>566631</v>
       </c>
       <c r="R4" t="n">
-        <v>6417084</v>
+        <v>6417076</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448826</v>
+        <v>122448814</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566628</v>
+        <v>566631</v>
       </c>
       <c r="R2" t="n">
-        <v>6417080</v>
+        <v>6417076</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448794</v>
+        <v>122448826</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566615</v>
+        <v>566628</v>
       </c>
       <c r="R3" t="n">
-        <v>6417084</v>
+        <v>6417080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448814</v>
+        <v>122448794</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566631</v>
+        <v>566615</v>
       </c>
       <c r="R4" t="n">
-        <v>6417076</v>
+        <v>6417084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448814</v>
+        <v>122448794</v>
       </c>
       <c r="B2" t="n">
         <v>98240</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566631</v>
+        <v>566615</v>
       </c>
       <c r="R2" t="n">
-        <v>6417076</v>
+        <v>6417084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448794</v>
+        <v>122448814</v>
       </c>
       <c r="B4" t="n">
         <v>98240</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566615</v>
+        <v>566631</v>
       </c>
       <c r="R4" t="n">
-        <v>6417084</v>
+        <v>6417076</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448794</v>
+        <v>122448814</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566615</v>
+        <v>566631</v>
       </c>
       <c r="R2" t="n">
-        <v>6417084</v>
+        <v>6417076</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
         <v>122448826</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448814</v>
+        <v>122448794</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566631</v>
+        <v>566615</v>
       </c>
       <c r="R4" t="n">
-        <v>6417076</v>
+        <v>6417084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122448814</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>122448826</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>122448794</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448814</v>
+        <v>122448794</v>
       </c>
       <c r="B2" t="n">
         <v>98244</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566631</v>
+        <v>566615</v>
       </c>
       <c r="R2" t="n">
-        <v>6417076</v>
+        <v>6417084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448826</v>
+        <v>122448814</v>
       </c>
       <c r="B3" t="n">
         <v>98244</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566628</v>
+        <v>566631</v>
       </c>
       <c r="R3" t="n">
-        <v>6417080</v>
+        <v>6417076</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448794</v>
+        <v>122448826</v>
       </c>
       <c r="B4" t="n">
         <v>98244</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566615</v>
+        <v>566628</v>
       </c>
       <c r="R4" t="n">
-        <v>6417084</v>
+        <v>6417080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448794</v>
+        <v>122448826</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566615</v>
+        <v>566628</v>
       </c>
       <c r="R2" t="n">
-        <v>6417084</v>
+        <v>6417080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448814</v>
+        <v>122448794</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566631</v>
+        <v>566615</v>
       </c>
       <c r="R3" t="n">
-        <v>6417076</v>
+        <v>6417084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448826</v>
+        <v>122448814</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566628</v>
+        <v>566631</v>
       </c>
       <c r="R4" t="n">
-        <v>6417080</v>
+        <v>6417076</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 961-2025 artfynd.xlsx
+++ b/artfynd/A 961-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448826</v>
+        <v>122448814</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566628</v>
+        <v>566631</v>
       </c>
       <c r="R2" t="n">
-        <v>6417080</v>
+        <v>6417076</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
         <v>122448794</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122448814</v>
+        <v>122448826</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566631</v>
+        <v>566628</v>
       </c>
       <c r="R4" t="n">
-        <v>6417076</v>
+        <v>6417080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
